--- a/artfynd/A 52620-2022 artfynd.xlsx
+++ b/artfynd/A 52620-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52620-2022 artfynd.xlsx
+++ b/artfynd/A 52620-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112392645</v>
       </c>
       <c r="B2" t="n">
-        <v>89806</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,7 +707,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Snottaberget (Snottaberget), Dlr</t>
+          <t>Snottaberget, Snottaberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -788,51 +783,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112393151</v>
+        <v>112392725</v>
       </c>
       <c r="B3" t="n">
-        <v>88737</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snottaberget (Snottaberget), Dlr</t>
+          <t>Snottaberget, Snottaberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509729</v>
+        <v>509995</v>
       </c>
       <c r="R3" t="n">
-        <v>6814194</v>
+        <v>6814167</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,51 +891,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112393218</v>
+        <v>112393151</v>
       </c>
       <c r="B4" t="n">
-        <v>89617</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snottaberget (Snottaberget), Dlr</t>
+          <t>Snottaberget, Snottaberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509697</v>
+        <v>509728</v>
       </c>
       <c r="R4" t="n">
-        <v>6814179</v>
+        <v>6814195</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,51 +999,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112393148</v>
+        <v>112393218</v>
       </c>
       <c r="B5" t="n">
-        <v>90957</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Snottaberget (Snottaberget), Dlr</t>
+          <t>Snottaberget, Snottaberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509729</v>
+        <v>509698</v>
       </c>
       <c r="R5" t="n">
-        <v>6814194</v>
+        <v>6814179</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,51 +1107,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112343568</v>
+        <v>112393148</v>
       </c>
       <c r="B6" t="n">
-        <v>90901</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232140</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Snottabo (Snottabo), Dlr</t>
+          <t>Snottaberget, Snottaberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510660</v>
+        <v>509728</v>
       </c>
       <c r="R6" t="n">
-        <v>6813980</v>
+        <v>6814195</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,22 +1173,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,51 +1215,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112343580</v>
+        <v>112343724</v>
       </c>
       <c r="B7" t="n">
-        <v>89747</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Snottabo (Snottabo), Dlr</t>
+          <t>Snottabo, Snottabo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510660</v>
+        <v>510716</v>
       </c>
       <c r="R7" t="n">
-        <v>6813980</v>
+        <v>6814045</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112344694</v>
+        <v>112343580</v>
       </c>
       <c r="B8" t="n">
-        <v>90836</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,35 +1334,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6055</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kanaltjärnen (Kanaltjärnen), Dlr</t>
+          <t>Snottabo, Snottabo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510393</v>
+        <v>510659</v>
       </c>
       <c r="R8" t="n">
-        <v>6813663</v>
+        <v>6813979</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,7 +1394,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1404,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,12 +1434,7 @@
         <v>112343573</v>
       </c>
       <c r="B9" t="n">
-        <v>90895</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,14 +1463,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Snottabo (Snottabo), Dlr</t>
+          <t>Snottabo, Snottabo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510660</v>
+        <v>510659</v>
       </c>
       <c r="R9" t="n">
-        <v>6813980</v>
+        <v>6813979</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1579,15 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112344707</v>
+        <v>112344694</v>
       </c>
       <c r="B10" t="n">
-        <v>90895</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,14 +1571,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kanaltjärnen (Kanaltjärnen), Dlr</t>
+          <t>Kanaltjärnen, Kanaltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510406</v>
+        <v>510393</v>
       </c>
       <c r="R10" t="n">
-        <v>6813691</v>
+        <v>6813663</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1692,51 +1647,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112343724</v>
+        <v>112344707</v>
       </c>
       <c r="B11" t="n">
-        <v>89920</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>6055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Snottabo (Snottabo), Dlr</t>
+          <t>Kanaltjärnen, Kanaltjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510716</v>
+        <v>510406</v>
       </c>
       <c r="R11" t="n">
-        <v>6814045</v>
+        <v>6813691</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,6 +1752,114 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112343568</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Snottabo, Snottabo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>510659</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6813979</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52620-2022 artfynd.xlsx
+++ b/artfynd/A 52620-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112392645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112392725</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112393151</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112393218</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112393148</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343724</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343580</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343573</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112344694</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112344707</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,8 +1915,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343568</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>